--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.21824960410386</v>
+        <v>0.5229655606668773</v>
       </c>
       <c r="D2" t="n">
-        <v>3.209009639169149</v>
+        <v>0.5214640663649868</v>
       </c>
       <c r="E2" t="n">
-        <v>38.80284173896069</v>
+        <v>6.305461782581111</v>
       </c>
       <c r="F2" t="n">
-        <v>38.71109997509765</v>
+        <v>6.290553745953367</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.85290211504086</v>
+        <v>11.83859659369414</v>
       </c>
       <c r="D3" t="n">
-        <v>72.58838878213149</v>
+        <v>11.79561317709637</v>
       </c>
       <c r="E3" t="n">
-        <v>38.80284173896069</v>
+        <v>6.305461782581111</v>
       </c>
       <c r="F3" t="n">
-        <v>38.71109997509765</v>
+        <v>6.290553745953367</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>94.05997901431846</v>
+        <v>15.28474658982675</v>
       </c>
       <c r="D4" t="n">
-        <v>93.87501552453287</v>
+        <v>15.25469002273659</v>
       </c>
       <c r="E4" t="n">
-        <v>38.80284173896069</v>
+        <v>6.305461782581111</v>
       </c>
       <c r="F4" t="n">
-        <v>38.71109997509765</v>
+        <v>6.290553745953367</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
